--- a/Task distribution.xlsx
+++ b/Task distribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My\Uni\2026\STAT394\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD54603E-B07A-4F6D-A9A1-C6CB5D0DFB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D91773-7781-4ADF-BBA3-A4D0AA773B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D161B614-2449-41DB-8C03-66F1AB07ABB3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Task</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>Riley</t>
+  </si>
+  <si>
+    <t>high-level description</t>
+  </si>
+  <si>
+    <t>descriptive analysis</t>
+  </si>
+  <si>
+    <t>graphical analysis</t>
+  </si>
+  <si>
+    <t>multivariate normal distribution confirmation</t>
+  </si>
+  <si>
+    <t>surprising observations</t>
+  </si>
+  <si>
+    <t>grouping of samples</t>
   </si>
 </sst>
 </file>
@@ -443,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C0520A-1470-4CA1-A75B-232F3FB1699E}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
@@ -495,6 +513,42 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
